--- a/test-data-loader/test-data.xlsx
+++ b/test-data-loader/test-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrew.roberts/IdeaProjects/laa-dces-drc-integration/test-data-loader/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDB98C2-D509-F84A-BED8-6938D8F41F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A9C227-8F59-FD47-8DF7-EEEEEB6A3100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="600" windowWidth="38400" windowHeight="23400" xr2:uid="{2749A602-8C44-BB47-9DDD-E70DD6A04286}"/>
+    <workbookView xWindow="38880" yWindow="600" windowWidth="38400" windowHeight="23400" xr2:uid="{2749A602-8C44-BB47-9DDD-E70DD6A04286}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
   <si>
     <t>Contrib Type</t>
   </si>
@@ -98,12 +98,6 @@
     <t>Duplicate new MAATID in same Batch</t>
   </si>
   <si>
-    <t>Contribution payloads found with Sentence Order Date &lt; 01-JAN-2001</t>
-  </si>
-  <si>
-    <t>Outcome is Appeal and the UpfrontContribution is empty or NULL</t>
-  </si>
-  <si>
     <t>Missing First Name.</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>effectiveDate = INVALID</t>
   </si>
   <si>
-    <t>incomeContributionCap = INVALID</t>
-  </si>
-  <si>
     <t>sufficientDeclaredEquity = INVALID</t>
   </si>
   <si>
@@ -191,9 +182,6 @@
     <t>MAATID Does Not Exist</t>
   </si>
   <si>
-    <t>Contribution payloads found with Sentence Order Date before 01-JAN-2001</t>
-  </si>
-  <si>
     <t>Fail - Paul setup data to force error</t>
   </si>
   <si>
@@ -221,9 +209,6 @@
     <t>Results 25/3 10:45</t>
   </si>
   <si>
-    <t>Check what values we put in there</t>
-  </si>
-  <si>
     <t>Fail - upfront was sent as 0</t>
   </si>
   <si>
@@ -243,6 +228,24 @@
   </si>
   <si>
     <t>Fail - Need to set caseType to APPEAL CC, and ccOutcome one of 3 values</t>
+  </si>
+  <si>
+    <t>Results 27/3 10:50</t>
+  </si>
+  <si>
+    <t>The sentence order date is earlier than the supported minimum date of 01-JAN-2001.</t>
+  </si>
+  <si>
+    <t>Outcome is set to Appeal but the upfront contribution value is missing.</t>
+  </si>
+  <si>
+    <t>Same values as 281877745</t>
+  </si>
+  <si>
+    <t>Results 27/3 12:10</t>
+  </si>
+  <si>
+    <t>incomeContributionCap = 1</t>
   </si>
 </sst>
 </file>
@@ -630,18 +633,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CC82C3-848B-574D-A2AB-68CAB97DCBAB}">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.6640625" customWidth="1"/>
+    <col min="2" max="2" width="71.6640625" customWidth="1"/>
     <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="50.6640625" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="26" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,13 +663,19 @@
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -679,13 +690,16 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -699,19 +713,24 @@
         <v>6391760</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C4" s="2">
         <v>281877745</v>
@@ -720,13 +739,15 @@
         <v>6393868</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -739,21 +760,25 @@
       <c r="D5" s="2">
         <v>6393868</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C6" s="2">
         <v>281755473</v>
@@ -762,21 +787,24 @@
         <v>6391763</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C7" s="2">
         <v>281755522</v>
@@ -785,21 +813,24 @@
         <v>6391764</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2">
         <v>281755985</v>
@@ -808,19 +839,24 @@
         <v>6391766</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2">
         <v>281900874</v>
@@ -829,15 +865,20 @@
         <v>6394049</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="C10" s="2">
         <v>281836067</v>
@@ -846,13 +887,15 @@
         <v>6393073</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -866,16 +909,19 @@
         <v>6391769</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -889,16 +935,19 @@
         <v>6391773</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -912,16 +961,19 @@
         <v>6391774</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -935,16 +987,19 @@
         <v>6391776</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -958,16 +1013,19 @@
         <v>6391777</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -981,19 +1039,22 @@
         <v>6391782</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -1007,16 +1068,19 @@
         <v>6391783</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -1030,16 +1094,19 @@
         <v>6391784</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1053,16 +1120,19 @@
         <v>6391788</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -1076,16 +1146,19 @@
         <v>6391791</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -1099,21 +1172,24 @@
         <v>6391798</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" s="2">
         <v>281757399</v>
@@ -1122,21 +1198,24 @@
         <v>6391802</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C23" s="2">
         <v>281757900</v>
@@ -1145,21 +1224,24 @@
         <v>6391806</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>40</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
       </c>
       <c r="C24" s="2">
         <v>281758430</v>
@@ -1168,45 +1250,48 @@
         <v>6391817</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" t="s">
         <v>45</v>
       </c>
-      <c r="E27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>46</v>
       </c>
-      <c r="E28" t="s">
+      <c r="B30" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.2">
